--- a/content/tz-obuchenie-v-kitae-dlya-russkih-posle-11-klassa.xlsx
+++ b/content/tz-obuchenie-v-kitae-dlya-russkih-posle-11-klassa.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Обучение в Китае для русских после 11 класса упирается не в список документов, а в календарь: вуз собирает заявки весной, а аттестат школа выдаёт в июне. Разбираем, чем закрывают это место в заявке, когда заказывать апостиль и перевод, что меняется, если на момент въезда вам ещё нет восемнадцати, и в каком порядке всё это делать, чтобы не потерять год.</t>
+          <t>Обучение в Китае для русских после 11 класса зависит не столько от списка документов, сколько от календаря: вуз собирает заявки весной, а аттестат школа выдаёт в июне. Разбираем, чем закрывают это место в заявке, когда заказывать апостиль и перевод, что меняется, если на момент въезда вам ещё нет восемнадцати, и в каком порядке всё это делать, чтобы не потерять год.</t>
         </is>
       </c>
     </row>
@@ -667,46 +667,58 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Целевой объём блока T123</t>
+          <t>Объём блока T123</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>37 000–40 000 знаков (лимит Tilda ≈ 50 000)</t>
+          <t>ПЛАН 37 000–40 000. ФАКТ 44 738 — выше плана, лимит 50 000 не нарушен</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция инфографики</t>
+          <t>Позиция инфографики</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>ПЛАН 26–31 %. ФАКТ 30,1 %</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция «Из личного опыта»</t>
+          <t>Позиция «Из личного опыта»</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>середина; при длинном хвосте FAQ допустимо 36–38 %</t>
+          <t>ПЛАН 36–38 %. ФАКТ 39,3 % — на 1,3 пункта выше вилки</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Позиция FAQ</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>75,5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Ключи по группам</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>После 11 класса, основная (10): обучение в китае для русских после 11 класса, учеба в китае после 11 класса для русских, поступление в китай после 11 класса, образование в китае для русских после 11 класса, вузы в китае для русских после 11 класса, как поступить в китай после 11, поступление в китай после 11, поступить в китай после 11, учеба в китае для русских после 11, вузы в китае для русских после 11 — тайтл, H1, вводная часть, H2 разделов 1 и 6, FAQ. Вузы и институты (3): китай поступление в вуз российским студентам, институт в китае для русских студентов, китайские институты для россиян — раздел про предварительное решение вуза и раздел про выбор программы. Бесплатно (5): учеба в китае для русских после 11 класса бесплатно, обучение в китае для русских после 11 класса бесплатно, поступление в китай после 11 класса бесплатно, поступить в китайский вуз бесплатно, учиться в китае после 11 класса из россии — раздел 5 плюс FAQ, без повтора трёх готовых разборов</t>
         </is>
@@ -723,12 +735,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -766,7 +778,11 @@
           <t>37 000–40 000, лимит ≈ 50 000</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>44 738 — ВЫШЕ ПЛАНА, лимит не нарушен, запас ≈ 5 000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -779,7 +795,11 @@
           <t>26–31 %</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>30,1 % — в норме</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -792,7 +812,11 @@
           <t>середина, допустимо 36–38 %</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>39,3 % — НА 1,3 ПУНКТА ВЫШЕ ВИЛКИ, но ближе к настоящей середине</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -800,8 +824,16 @@
           <t>Позиция FAQ</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>75,5 %</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -814,7 +846,11 @@
           <t>A = B</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>22 / 22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -827,7 +863,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -840,7 +880,11 @@
           <t>position: sticky, top 90</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sticky, top 90px</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -853,7 +897,11 @@
           <t>static, order 2, нет горизонтальной прокрутки</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>static, order 2, ширина документа 390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -866,7 +914,11 @@
           <t>да</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да: BlogPosting, Person, EducationalOrganization, FAQPage, BreadcrumbList</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -879,7 +931,11 @@
           <t>совпадение полное</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>6 вопросов и 6 ответов, совпадение полное</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -892,7 +948,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0; ёлочек 4 пары</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -905,7 +965,11 @@
           <t>все верны</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>найдена и исправлена одна: «про подготовка к HSK 4» → «про подготовку к HSK 4»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -918,29 +982,62 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>найдено и исправлено семь, см. лист Картинки и файл ТЗ в формате md</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
+          <t>Высота инфографики</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>подбирается замером</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>470 px при содержимом до 448, запас 22</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Дефекты рендеров</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>0 на отдаче</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>найдено и исправлено семь, перечислены на листе Картинки</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Адреса Tilda вшиты</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>7 в исходнике / 5 в блоке, assets = 0</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>ждём ссылки от заказчика</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1633,7 +1730,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Обучение в Китае для русских после 11 класса упирается не в список документов, а в календарь: вуз собирает заявки весной, а аттестат школа выдаёт в июне. Разбираем, чем закрывают это место в заявке, когда заказывать апостиль и перевод, что меняется, если на момент въезда вам ещё нет восемнадцати, и в каком порядке всё это делать, чтобы не потерять год.</t>
+          <t>Обучение в Китае для русских после 11 класса зависит не столько от списка документов, сколько от календаря: вуз собирает заявки весной, а аттестат школа выдаёт в июне. Разбираем, чем закрывают это место в заявке, когда заказывать апостиль и перевод, что меняется, если на момент въезда вам ещё нет восемнадцати, и в каком порядке всё это делать, чтобы не потерять год.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1968,13 +2065,119 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
+          <t>ДЕФЕКТ 1. Обложка</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>заголовок рассыпался на четыре строки со словом-сиротой «марте»</t>
+        </is>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>проставляется после просмотра</t>
+          <t>кегль 45 → 42 px, колонка 340 → 372 px, запрет переносов, явный разрыв строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 2. Обложка</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>дуга-стрелка приземлялась мимо календарей, в пустое поле</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>svg привязан к ширине пары календарей, концы поставлены по центрам: 123 и 413 px</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 3. Обложка</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>подписи «дедлайн вуза» и «аттестат» стояли на разной высоте: в марте шесть рядов сетки, в июне пять</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>сетке задано шесть рядов всегда, низы карточек выровнены</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 4. Инфографика</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>БРУСНИЧНАЯ ПОЛОСА НЕ ОТРИСОВАЛАСЬ СОВСЕМ — схлопнулась в одну пунктирную линию у левого края</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>причина: в calc() процент умножался на процент, вся декларация была невалидной. Заведён отдельный слой-трек, полоса позиционируется внутри него в обычных процентах</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 5. Инфографика</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>подписи «аттестат на руках», «решение вуза», «набор открыт» пересекали границы полосы и читались неверно</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>добавлено выравнивание подписи по левому краю от точки</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 6. Инфографика</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>заголовок ломался так, что «совпадают» оставалось одно на строке</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>явный разрыв строки перед курсивом</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 7. Инфографика</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>холст переполнялся на 2 px</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>высота подобрана замером: 470 px при содержимом до 448</t>
         </is>
       </c>
     </row>

--- a/content/tz-obuchenie-v-kitae-dlya-russkih-posle-11-klassa.xlsx
+++ b/content/tz-obuchenie-v-kitae-dlya-russkih-posle-11-klassa.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН 37 000–40 000. ФАКТ 44 738 — выше плана, лимит 50 000 не нарушен</t>
+          <t>ПЛАН 37 000–40 000. ФАКТ 44 901 с адресами Tilda — выше плана, лимит 50 000 не нарушен, запас 5 099</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>44 738 — ВЫШЕ ПЛАНА, лимит не нарушен, запас ≈ 5 000</t>
+          <t>44 901 с адресами Tilda — ВЫШЕ ПЛАНА, лимит не нарушен, запас 5 099</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>ждём ссылки от заказчика</t>
+          <t>7 / 5, assets = 0 — вшиты</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com — подставляется после загрузки</t>
+          <t>https://static.tildacdn.com/tild6134-3362-4238-a433-663738633164/obuchenie-v-kitae-dl.png</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com</t>
+          <t>https://static.tildacdn.com/tild6134-3362-4238-a433-663738633164/obuchenie-v-kitae-dl.png</t>
         </is>
       </c>
     </row>
